--- a/en/data-mobilization/modules/ROOT/attachments/UC-Practice-3-ForPublication.xlsx
+++ b/en/data-mobilization/modules/ROOT/attachments/UC-Practice-3-ForPublication.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mwg756/Downloads/data-mobilization-v2/attachments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B05F00-E291-B144-89CA-46D5028DDAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E4D2EB-5273-0348-8247-99C925F8D6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14320" xr2:uid="{A16DD252-91C3-C149-B0EA-EAAC784FD77A}"/>
   </bookViews>
@@ -16,20 +16,19 @@
     <sheet name="butterfly-event" sheetId="1" r:id="rId1"/>
     <sheet name="butterfly-EMof" sheetId="3" r:id="rId2"/>
     <sheet name="butterfly-humboldt" sheetId="5" r:id="rId3"/>
-    <sheet name="butterfly-occurrence" sheetId="2" r:id="rId4"/>
+    <sheet name="butterfly-occurrence" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'butterfly-EMof'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'butterfly-event'!$A$1:$AC$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'butterfly-humboldt'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'butterfly-occurrence'!$A$1:$P$305</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="373">
   <si>
     <t>language</t>
   </si>
@@ -328,9 +327,6 @@
     <t>Citronfjäril</t>
   </si>
   <si>
-    <t>Heliconiinae</t>
-  </si>
-  <si>
     <t>Obestämd pärlemorfjäril</t>
   </si>
   <si>
@@ -1034,13 +1030,130 @@
   </si>
   <si>
     <t>13:37+02:00/15:40+02:00</t>
+  </si>
+  <si>
+    <t>kingdom</t>
+  </si>
+  <si>
+    <t>phylum</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Animalia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Arthropoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Insecta</t>
+  </si>
+  <si>
+    <t>Nymphalidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lycaenidae</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hesperiidae</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pieridae</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Heliconiidae</t>
+  </si>
+  <si>
+    <t>Arthropoda</t>
+  </si>
+  <si>
+    <t>Insecta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Zygaenidae</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1171,12 +1284,6 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1523,9 +1630,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1939,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1" t="s">
         <v>281</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>282</v>
       </c>
-      <c r="F1" t="s">
-        <v>283</v>
-      </c>
       <c r="G1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1" t="s">
         <v>9</v>
@@ -1996,13 +2104,13 @@
         <v>3</v>
       </c>
       <c r="W1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="X1" t="s">
         <v>4</v>
       </c>
       <c r="Y1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Z1" t="s">
         <v>5</v>
@@ -2010,28 +2118,28 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="1">
         <v>41095</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K2" t="s">
         <v>22</v>
@@ -2064,19 +2172,19 @@
         <v>21</v>
       </c>
       <c r="U2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W2" t="s">
+        <v>271</v>
+      </c>
+      <c r="X2" t="s">
         <v>272</v>
       </c>
-      <c r="X2" t="s">
-        <v>273</v>
-      </c>
       <c r="Y2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z2" t="s">
         <v>28</v>
@@ -2084,28 +2192,28 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B3" s="1">
         <v>45115</v>
       </c>
       <c r="C3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K3" t="s">
         <v>22</v>
@@ -2138,19 +2246,19 @@
         <v>21</v>
       </c>
       <c r="U3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W3" t="s">
+        <v>271</v>
+      </c>
+      <c r="X3" t="s">
         <v>272</v>
       </c>
-      <c r="X3" t="s">
-        <v>273</v>
-      </c>
       <c r="Y3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z3" t="s">
         <v>28</v>
@@ -2158,28 +2266,28 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4" s="1">
         <v>43664</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K4" t="s">
         <v>22</v>
@@ -2212,19 +2320,19 @@
         <v>21</v>
       </c>
       <c r="U4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W4" t="s">
+        <v>271</v>
+      </c>
+      <c r="X4" t="s">
         <v>272</v>
       </c>
-      <c r="X4" t="s">
-        <v>273</v>
-      </c>
       <c r="Y4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z4" t="s">
         <v>28</v>
@@ -2232,28 +2340,28 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" s="1">
         <v>40733</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K5" t="s">
         <v>22</v>
@@ -2286,19 +2394,19 @@
         <v>21</v>
       </c>
       <c r="U5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W5" t="s">
+        <v>271</v>
+      </c>
+      <c r="X5" t="s">
         <v>272</v>
       </c>
-      <c r="X5" t="s">
-        <v>273</v>
-      </c>
       <c r="Y5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z5" t="s">
         <v>28</v>
@@ -2306,28 +2414,28 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B6" s="1">
         <v>40743</v>
       </c>
       <c r="C6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K6" t="s">
         <v>22</v>
@@ -2360,19 +2468,19 @@
         <v>21</v>
       </c>
       <c r="U6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W6" t="s">
+        <v>271</v>
+      </c>
+      <c r="X6" t="s">
         <v>272</v>
       </c>
-      <c r="X6" t="s">
-        <v>273</v>
-      </c>
       <c r="Y6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z6" t="s">
         <v>28</v>
@@ -2380,28 +2488,28 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B7" s="1">
         <v>42922</v>
       </c>
       <c r="C7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K7" t="s">
         <v>22</v>
@@ -2434,19 +2542,19 @@
         <v>21</v>
       </c>
       <c r="U7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W7" t="s">
+        <v>271</v>
+      </c>
+      <c r="X7" t="s">
         <v>272</v>
       </c>
-      <c r="X7" t="s">
-        <v>273</v>
-      </c>
       <c r="Y7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z7" t="s">
         <v>28</v>
@@ -2454,28 +2562,28 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="1">
         <v>42561</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K8" t="s">
         <v>22</v>
@@ -2508,19 +2616,19 @@
         <v>21</v>
       </c>
       <c r="U8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W8" t="s">
+        <v>271</v>
+      </c>
+      <c r="X8" t="s">
         <v>272</v>
       </c>
-      <c r="X8" t="s">
-        <v>273</v>
-      </c>
       <c r="Y8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z8" t="s">
         <v>28</v>
@@ -2528,34 +2636,34 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B9" s="1">
         <v>42186</v>
       </c>
       <c r="C9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D9">
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H9" t="s">
         <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K9" t="s">
         <v>22</v>
@@ -2588,19 +2696,19 @@
         <v>21</v>
       </c>
       <c r="U9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W9" t="s">
+        <v>271</v>
+      </c>
+      <c r="X9" t="s">
         <v>272</v>
       </c>
-      <c r="X9" t="s">
-        <v>273</v>
-      </c>
       <c r="Y9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z9" t="s">
         <v>28</v>
@@ -2608,28 +2716,28 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="1">
         <v>41466</v>
       </c>
       <c r="C10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K10" t="s">
         <v>22</v>
@@ -2662,19 +2770,19 @@
         <v>21</v>
       </c>
       <c r="U10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W10" t="s">
+        <v>271</v>
+      </c>
+      <c r="X10" t="s">
         <v>272</v>
       </c>
-      <c r="X10" t="s">
-        <v>273</v>
-      </c>
       <c r="Y10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z10" t="s">
         <v>28</v>
@@ -2682,28 +2790,28 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B11" s="1">
         <v>43278</v>
       </c>
       <c r="C11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K11" t="s">
         <v>22</v>
@@ -2736,19 +2844,19 @@
         <v>21</v>
       </c>
       <c r="U11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W11" t="s">
+        <v>271</v>
+      </c>
+      <c r="X11" t="s">
         <v>272</v>
       </c>
-      <c r="X11" t="s">
-        <v>273</v>
-      </c>
       <c r="Y11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z11" t="s">
         <v>28</v>
@@ -2776,514 +2884,514 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" t="s">
         <v>153</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>154</v>
       </c>
-      <c r="D1" t="s">
-        <v>155</v>
-      </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" t="s">
         <v>306</v>
-      </c>
-      <c r="C2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E3" t="s">
         <v>308</v>
-      </c>
-      <c r="E3" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" t="s">
         <v>310</v>
-      </c>
-      <c r="E4" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E5" t="s">
         <v>312</v>
-      </c>
-      <c r="E5" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" t="s">
         <v>314</v>
-      </c>
-      <c r="E6" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C7">
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C10">
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C12">
         <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C14">
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C16">
         <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C19">
         <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C23">
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E26" t="s">
         <v>312</v>
-      </c>
-      <c r="E26" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C28">
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C30">
         <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C31">
         <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C33">
         <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C36">
         <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C37" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
+        <v>309</v>
+      </c>
+      <c r="E38" t="s">
         <v>310</v>
-      </c>
-      <c r="E38" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C39">
         <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3320,57 +3428,57 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" t="s">
         <v>298</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1" t="s">
         <v>299</v>
       </c>
-      <c r="D1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G1" t="s">
-        <v>278</v>
-      </c>
-      <c r="H1" t="s">
-        <v>280</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>300</v>
       </c>
-      <c r="J1" t="s">
-        <v>301</v>
-      </c>
       <c r="K1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L1" t="s">
+        <v>288</v>
+      </c>
+      <c r="M1" t="s">
         <v>289</v>
       </c>
-      <c r="M1" t="s">
-        <v>290</v>
-      </c>
       <c r="N1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" t="s">
         <v>317</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>318</v>
-      </c>
-      <c r="F2" t="s">
-        <v>319</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -3379,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -3391,24 +3499,24 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" t="s">
         <v>317</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>318</v>
-      </c>
-      <c r="F3" t="s">
-        <v>319</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -3417,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -3429,24 +3537,24 @@
         <v>2</v>
       </c>
       <c r="M3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" t="s">
         <v>317</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>318</v>
-      </c>
-      <c r="F4" t="s">
-        <v>319</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -3455,10 +3563,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -3467,24 +3575,24 @@
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" t="s">
         <v>317</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>318</v>
-      </c>
-      <c r="F5" t="s">
-        <v>319</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -3493,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -3505,24 +3613,24 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E6" t="s">
         <v>317</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>318</v>
-      </c>
-      <c r="F6" t="s">
-        <v>319</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -3531,10 +3639,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -3543,24 +3651,24 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E7" t="s">
         <v>317</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>318</v>
-      </c>
-      <c r="F7" t="s">
-        <v>319</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -3569,10 +3677,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -3581,24 +3689,24 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E8" t="s">
         <v>317</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>318</v>
-      </c>
-      <c r="F8" t="s">
-        <v>319</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -3607,10 +3715,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -3619,30 +3727,30 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B9">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -3651,10 +3759,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -3663,24 +3771,24 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
+        <v>316</v>
+      </c>
+      <c r="E10" t="s">
         <v>317</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>318</v>
-      </c>
-      <c r="F10" t="s">
-        <v>319</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -3689,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -3701,24 +3809,24 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="s">
+        <v>316</v>
+      </c>
+      <c r="E11" t="s">
         <v>317</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>318</v>
-      </c>
-      <c r="F11" t="s">
-        <v>319</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -3727,10 +3835,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -3739,10 +3847,10 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3751,2603 +3859,3941 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3AEF68-70B2-A143-B97E-63076AA12B25}">
-  <dimension ref="A1:I89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C0901EA-C68F-9B4E-B7EB-0D9654F92814}">
+  <dimension ref="A1:N89"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="82" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39" customWidth="1"/>
     <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H60" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4">
-        <v>334</v>
-      </c>
-      <c r="D4">
-        <v>334</v>
-      </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H61" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H62" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I82" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N82" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C5">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="C88" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H88" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13">
-        <v>9</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>210</v>
-      </c>
-      <c r="C14">
-        <v>21</v>
-      </c>
-      <c r="D14">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" t="s">
-        <v>93</v>
-      </c>
-      <c r="I14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>168</v>
-      </c>
-      <c r="B15" t="s">
-        <v>211</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C16">
-        <v>23</v>
-      </c>
-      <c r="D16">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>168</v>
-      </c>
-      <c r="B18" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18">
-        <v>94</v>
-      </c>
-      <c r="D18">
-        <v>94</v>
-      </c>
-      <c r="E18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B19" t="s">
-        <v>229</v>
-      </c>
-      <c r="C19">
-        <v>26</v>
-      </c>
-      <c r="D19">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" t="s">
-        <v>117</v>
-      </c>
-      <c r="I19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C20">
-        <v>307</v>
-      </c>
-      <c r="D20">
-        <v>307</v>
-      </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>168</v>
-      </c>
-      <c r="B21" t="s">
-        <v>236</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" t="s">
-        <v>124</v>
-      </c>
-      <c r="I21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" t="s">
-        <v>239</v>
-      </c>
-      <c r="C22">
-        <v>11</v>
-      </c>
-      <c r="D22">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" t="s">
-        <v>128</v>
-      </c>
-      <c r="I23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B24" t="s">
-        <v>244</v>
-      </c>
-      <c r="C24">
-        <v>5</v>
-      </c>
-      <c r="D24">
-        <v>5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" t="s">
-        <v>130</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="H89" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" t="s">
-        <v>246</v>
-      </c>
-      <c r="C25">
-        <v>52</v>
-      </c>
-      <c r="D25">
-        <v>52</v>
-      </c>
-      <c r="E25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" t="s">
-        <v>134</v>
-      </c>
-      <c r="I25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" t="s">
-        <v>251</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" t="s">
-        <v>53</v>
-      </c>
-      <c r="H26" t="s">
-        <v>140</v>
-      </c>
-      <c r="I26" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>168</v>
-      </c>
-      <c r="B27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C27">
-        <v>20</v>
-      </c>
-      <c r="D27">
-        <v>20</v>
-      </c>
-      <c r="E27" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>168</v>
-      </c>
-      <c r="B28" t="s">
-        <v>257</v>
-      </c>
-      <c r="C28">
-        <v>15</v>
-      </c>
-      <c r="D28">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" t="s">
-        <v>144</v>
-      </c>
-      <c r="I28" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" t="s">
-        <v>260</v>
-      </c>
-      <c r="C29">
-        <v>10</v>
-      </c>
-      <c r="D29">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H29" t="s">
-        <v>146</v>
-      </c>
-      <c r="I29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>163</v>
-      </c>
-      <c r="B30" t="s">
-        <v>172</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" t="s">
-        <v>57</v>
-      </c>
-      <c r="H30" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" t="s">
-        <v>57</v>
-      </c>
-      <c r="H31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>163</v>
-      </c>
-      <c r="B32" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>163</v>
-      </c>
-      <c r="B33" t="s">
-        <v>181</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>51</v>
-      </c>
-      <c r="F33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" t="s">
-        <v>62</v>
-      </c>
-      <c r="I33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>163</v>
-      </c>
-      <c r="B34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" t="s">
-        <v>186</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" t="s">
-        <v>69</v>
-      </c>
-      <c r="I35" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" t="s">
-        <v>187</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" t="s">
-        <v>71</v>
-      </c>
-      <c r="I36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>163</v>
-      </c>
-      <c r="B37" t="s">
-        <v>193</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" t="s">
-        <v>52</v>
-      </c>
-      <c r="G37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" t="s">
-        <v>77</v>
-      </c>
-      <c r="I37" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>163</v>
-      </c>
-      <c r="B38" t="s">
-        <v>196</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>51</v>
-      </c>
-      <c r="F38" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" t="s">
-        <v>79</v>
-      </c>
-      <c r="I38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>163</v>
-      </c>
-      <c r="B39" t="s">
-        <v>199</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39" t="s">
-        <v>52</v>
-      </c>
-      <c r="G39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" t="s">
-        <v>81</v>
-      </c>
-      <c r="I39" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>163</v>
-      </c>
-      <c r="B40" t="s">
-        <v>200</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" t="s">
-        <v>52</v>
-      </c>
-      <c r="G40" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" t="s">
-        <v>83</v>
-      </c>
-      <c r="I40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>163</v>
-      </c>
-      <c r="B41" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" t="s">
-        <v>52</v>
-      </c>
-      <c r="G41" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" t="s">
-        <v>85</v>
-      </c>
-      <c r="I41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>163</v>
-      </c>
-      <c r="B42" t="s">
-        <v>205</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42" t="s">
-        <v>52</v>
-      </c>
-      <c r="G42" t="s">
-        <v>57</v>
-      </c>
-      <c r="H42" t="s">
-        <v>89</v>
-      </c>
-      <c r="I42" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>163</v>
-      </c>
-      <c r="B43" t="s">
-        <v>208</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>51</v>
-      </c>
-      <c r="F43" t="s">
-        <v>52</v>
-      </c>
-      <c r="G43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" t="s">
-        <v>91</v>
-      </c>
-      <c r="I43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>163</v>
-      </c>
-      <c r="B44" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>51</v>
-      </c>
-      <c r="F44" t="s">
-        <v>52</v>
-      </c>
-      <c r="G44" t="s">
-        <v>57</v>
-      </c>
-      <c r="H44" t="s">
-        <v>97</v>
-      </c>
-      <c r="I44" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>163</v>
-      </c>
-      <c r="B45" t="s">
-        <v>218</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" t="s">
-        <v>52</v>
-      </c>
-      <c r="G45" t="s">
-        <v>57</v>
-      </c>
-      <c r="H45" t="s">
-        <v>105</v>
-      </c>
-      <c r="I45" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>163</v>
-      </c>
-      <c r="B46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>51</v>
-      </c>
-      <c r="F46" t="s">
-        <v>52</v>
-      </c>
-      <c r="G46" t="s">
-        <v>57</v>
-      </c>
-      <c r="H46" t="s">
-        <v>107</v>
-      </c>
-      <c r="I46" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>163</v>
-      </c>
-      <c r="B47" t="s">
-        <v>223</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" t="s">
-        <v>52</v>
-      </c>
-      <c r="G47" t="s">
-        <v>57</v>
-      </c>
-      <c r="H47" t="s">
-        <v>111</v>
-      </c>
-      <c r="I47" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>163</v>
-      </c>
-      <c r="B48" t="s">
-        <v>224</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>51</v>
-      </c>
-      <c r="F48" t="s">
-        <v>52</v>
-      </c>
-      <c r="G48" t="s">
-        <v>57</v>
-      </c>
-      <c r="H48" t="s">
-        <v>113</v>
-      </c>
-      <c r="I48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>163</v>
-      </c>
-      <c r="B49" t="s">
-        <v>225</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" t="s">
-        <v>52</v>
-      </c>
-      <c r="G49" t="s">
-        <v>57</v>
-      </c>
-      <c r="H49" t="s">
-        <v>115</v>
-      </c>
-      <c r="I49" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>163</v>
-      </c>
-      <c r="B50" t="s">
-        <v>227</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>51</v>
-      </c>
-      <c r="F50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G50" t="s">
-        <v>57</v>
-      </c>
-      <c r="H50" t="s">
-        <v>117</v>
-      </c>
-      <c r="I50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>163</v>
-      </c>
-      <c r="B51" t="s">
-        <v>230</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>51</v>
-      </c>
-      <c r="F51" t="s">
-        <v>52</v>
-      </c>
-      <c r="G51" t="s">
-        <v>57</v>
-      </c>
-      <c r="H51" t="s">
-        <v>119</v>
-      </c>
-      <c r="I51" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>163</v>
-      </c>
-      <c r="B52" t="s">
-        <v>233</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52" t="s">
-        <v>51</v>
-      </c>
-      <c r="F52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G52" t="s">
-        <v>57</v>
-      </c>
-      <c r="H52" t="s">
-        <v>121</v>
-      </c>
-      <c r="I52" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>163</v>
-      </c>
-      <c r="B53" t="s">
-        <v>237</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>51</v>
-      </c>
-      <c r="F53" t="s">
-        <v>52</v>
-      </c>
-      <c r="G53" t="s">
-        <v>57</v>
-      </c>
-      <c r="H53" t="s">
-        <v>126</v>
-      </c>
-      <c r="I53" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" t="s">
-        <v>240</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
-        <v>51</v>
-      </c>
-      <c r="F54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G54" t="s">
-        <v>57</v>
-      </c>
-      <c r="H54" t="s">
-        <v>128</v>
-      </c>
-      <c r="I54" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>163</v>
-      </c>
-      <c r="B55" t="s">
-        <v>243</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>51</v>
-      </c>
-      <c r="F55" t="s">
-        <v>52</v>
-      </c>
-      <c r="G55" t="s">
-        <v>57</v>
-      </c>
-      <c r="H55" t="s">
-        <v>130</v>
-      </c>
-      <c r="I55" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>163</v>
-      </c>
-      <c r="B56" t="s">
-        <v>247</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F56" t="s">
-        <v>52</v>
-      </c>
-      <c r="G56" t="s">
-        <v>57</v>
-      </c>
-      <c r="H56" t="s">
-        <v>136</v>
-      </c>
-      <c r="I56" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>163</v>
-      </c>
-      <c r="B57" t="s">
-        <v>252</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" t="s">
-        <v>51</v>
-      </c>
-      <c r="F57" t="s">
-        <v>52</v>
-      </c>
-      <c r="G57" t="s">
-        <v>57</v>
-      </c>
-      <c r="H57" t="s">
-        <v>142</v>
-      </c>
-      <c r="I57" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" t="s">
-        <v>255</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>51</v>
-      </c>
-      <c r="F58" t="s">
-        <v>52</v>
-      </c>
-      <c r="G58" t="s">
-        <v>57</v>
-      </c>
-      <c r="H58" t="s">
-        <v>144</v>
-      </c>
-      <c r="I58" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>163</v>
-      </c>
-      <c r="B59" t="s">
-        <v>258</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>51</v>
-      </c>
-      <c r="F59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G59" t="s">
-        <v>57</v>
-      </c>
-      <c r="H59" t="s">
-        <v>146</v>
-      </c>
-      <c r="I59" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>165</v>
-      </c>
-      <c r="B60" t="s">
-        <v>175</v>
-      </c>
-      <c r="C60">
-        <v>4</v>
-      </c>
-      <c r="D60">
-        <v>4</v>
-      </c>
-      <c r="E60" t="s">
-        <v>51</v>
-      </c>
-      <c r="F60" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60" t="s">
-        <v>53</v>
-      </c>
-      <c r="H60" t="s">
-        <v>58</v>
-      </c>
-      <c r="I60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>165</v>
-      </c>
-      <c r="B61" t="s">
-        <v>184</v>
-      </c>
-      <c r="C61">
-        <v>40</v>
-      </c>
-      <c r="D61">
-        <v>40</v>
-      </c>
-      <c r="E61" t="s">
-        <v>51</v>
-      </c>
-      <c r="F61" t="s">
-        <v>52</v>
-      </c>
-      <c r="G61" t="s">
-        <v>53</v>
-      </c>
-      <c r="H61" t="s">
-        <v>67</v>
-      </c>
-      <c r="I61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>165</v>
-      </c>
-      <c r="B62" t="s">
-        <v>188</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>51</v>
-      </c>
-      <c r="F62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G62" t="s">
-        <v>53</v>
-      </c>
-      <c r="H62" t="s">
-        <v>71</v>
-      </c>
-      <c r="I62" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>165</v>
-      </c>
-      <c r="B63" t="s">
-        <v>190</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>51</v>
-      </c>
-      <c r="F63" t="s">
-        <v>52</v>
-      </c>
-      <c r="G63" t="s">
-        <v>53</v>
-      </c>
-      <c r="H63" t="s">
-        <v>73</v>
-      </c>
-      <c r="I63" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>165</v>
-      </c>
-      <c r="B64" t="s">
-        <v>194</v>
-      </c>
-      <c r="C64">
-        <v>2</v>
-      </c>
-      <c r="D64">
-        <v>2</v>
-      </c>
-      <c r="E64" t="s">
-        <v>51</v>
-      </c>
-      <c r="F64" t="s">
-        <v>52</v>
-      </c>
-      <c r="G64" t="s">
-        <v>53</v>
-      </c>
-      <c r="H64" t="s">
-        <v>77</v>
-      </c>
-      <c r="I64" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>165</v>
-      </c>
-      <c r="B65" t="s">
-        <v>197</v>
-      </c>
-      <c r="C65">
-        <v>10</v>
-      </c>
-      <c r="D65">
-        <v>10</v>
-      </c>
-      <c r="E65" t="s">
-        <v>51</v>
-      </c>
-      <c r="F65" t="s">
-        <v>52</v>
-      </c>
-      <c r="G65" t="s">
-        <v>53</v>
-      </c>
-      <c r="H65" t="s">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>165</v>
-      </c>
-      <c r="B66" t="s">
-        <v>201</v>
-      </c>
-      <c r="C66">
-        <v>11</v>
-      </c>
-      <c r="D66">
-        <v>11</v>
-      </c>
-      <c r="E66" t="s">
-        <v>51</v>
-      </c>
-      <c r="F66" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66" t="s">
-        <v>53</v>
-      </c>
-      <c r="H66" t="s">
-        <v>83</v>
-      </c>
-      <c r="I66" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>165</v>
-      </c>
-      <c r="B67" t="s">
-        <v>206</v>
-      </c>
-      <c r="C67">
-        <v>2</v>
-      </c>
-      <c r="D67">
-        <v>2</v>
-      </c>
-      <c r="E67" t="s">
-        <v>51</v>
-      </c>
-      <c r="F67" t="s">
-        <v>52</v>
-      </c>
-      <c r="G67" t="s">
-        <v>53</v>
-      </c>
-      <c r="H67" t="s">
-        <v>89</v>
-      </c>
-      <c r="I67" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>165</v>
-      </c>
-      <c r="B68" t="s">
-        <v>213</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
-        <v>51</v>
-      </c>
-      <c r="F68" t="s">
-        <v>52</v>
-      </c>
-      <c r="G68" t="s">
-        <v>53</v>
-      </c>
-      <c r="H68" t="s">
-        <v>97</v>
-      </c>
-      <c r="I68" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>165</v>
-      </c>
-      <c r="B69" t="s">
-        <v>215</v>
-      </c>
-      <c r="C69">
-        <v>15</v>
-      </c>
-      <c r="D69">
-        <v>15</v>
-      </c>
-      <c r="E69" t="s">
-        <v>51</v>
-      </c>
-      <c r="F69" t="s">
-        <v>52</v>
-      </c>
-      <c r="G69" t="s">
-        <v>53</v>
-      </c>
-      <c r="H69" t="s">
-        <v>99</v>
-      </c>
-      <c r="I69" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>165</v>
-      </c>
-      <c r="B70" t="s">
-        <v>216</v>
-      </c>
-      <c r="C70">
-        <v>2</v>
-      </c>
-      <c r="D70">
-        <v>2</v>
-      </c>
-      <c r="E70" t="s">
-        <v>51</v>
-      </c>
-      <c r="F70" t="s">
-        <v>52</v>
-      </c>
-      <c r="G70" t="s">
-        <v>53</v>
-      </c>
-      <c r="H70" t="s">
-        <v>101</v>
-      </c>
-      <c r="I70" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>165</v>
-      </c>
-      <c r="B71" t="s">
-        <v>219</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>51</v>
-      </c>
-      <c r="F71" t="s">
-        <v>52</v>
-      </c>
-      <c r="G71" t="s">
-        <v>53</v>
-      </c>
-      <c r="H71" t="s">
-        <v>105</v>
-      </c>
-      <c r="I71" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>165</v>
-      </c>
-      <c r="B72" t="s">
-        <v>222</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>51</v>
-      </c>
-      <c r="F72" t="s">
-        <v>52</v>
-      </c>
-      <c r="G72" t="s">
-        <v>53</v>
-      </c>
-      <c r="H72" t="s">
-        <v>109</v>
-      </c>
-      <c r="I72" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>165</v>
-      </c>
-      <c r="B73" t="s">
-        <v>226</v>
-      </c>
-      <c r="C73">
-        <v>69</v>
-      </c>
-      <c r="D73">
-        <v>69</v>
-      </c>
-      <c r="E73" t="s">
-        <v>51</v>
-      </c>
-      <c r="F73" t="s">
-        <v>52</v>
-      </c>
-      <c r="G73" t="s">
-        <v>53</v>
-      </c>
-      <c r="H73" t="s">
-        <v>115</v>
-      </c>
-      <c r="I73" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>165</v>
-      </c>
-      <c r="B74" t="s">
-        <v>228</v>
-      </c>
-      <c r="C74">
-        <v>12</v>
-      </c>
-      <c r="D74">
-        <v>12</v>
-      </c>
-      <c r="E74" t="s">
-        <v>51</v>
-      </c>
-      <c r="F74" t="s">
-        <v>52</v>
-      </c>
-      <c r="G74" t="s">
-        <v>53</v>
-      </c>
-      <c r="H74" t="s">
-        <v>117</v>
-      </c>
-      <c r="I74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" t="s">
-        <v>231</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>51</v>
-      </c>
-      <c r="F75" t="s">
-        <v>52</v>
-      </c>
-      <c r="G75" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" t="s">
-        <v>119</v>
-      </c>
-      <c r="I75" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>165</v>
-      </c>
-      <c r="B76" t="s">
-        <v>234</v>
-      </c>
-      <c r="C76">
-        <v>6</v>
-      </c>
-      <c r="D76">
-        <v>6</v>
-      </c>
-      <c r="E76" t="s">
-        <v>51</v>
-      </c>
-      <c r="F76" t="s">
-        <v>52</v>
-      </c>
-      <c r="G76" t="s">
-        <v>53</v>
-      </c>
-      <c r="H76" t="s">
-        <v>63</v>
-      </c>
-      <c r="I76" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" t="s">
-        <v>235</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77" t="s">
-        <v>51</v>
-      </c>
-      <c r="F77" t="s">
-        <v>52</v>
-      </c>
-      <c r="G77" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" t="s">
-        <v>124</v>
-      </c>
-      <c r="I77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>165</v>
-      </c>
-      <c r="B78" t="s">
-        <v>238</v>
-      </c>
-      <c r="C78">
-        <v>4</v>
-      </c>
-      <c r="D78">
-        <v>4</v>
-      </c>
-      <c r="E78" t="s">
-        <v>51</v>
-      </c>
-      <c r="F78" t="s">
-        <v>52</v>
-      </c>
-      <c r="G78" t="s">
-        <v>53</v>
-      </c>
-      <c r="H78" t="s">
-        <v>126</v>
-      </c>
-      <c r="I78" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>165</v>
-      </c>
-      <c r="B79" t="s">
-        <v>241</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79" t="s">
-        <v>51</v>
-      </c>
-      <c r="F79" t="s">
-        <v>52</v>
-      </c>
-      <c r="G79" t="s">
-        <v>53</v>
-      </c>
-      <c r="H79" t="s">
-        <v>128</v>
-      </c>
-      <c r="I79" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>165</v>
-      </c>
-      <c r="B80" t="s">
-        <v>245</v>
-      </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80" t="s">
-        <v>51</v>
-      </c>
-      <c r="F80" t="s">
-        <v>52</v>
-      </c>
-      <c r="G80" t="s">
-        <v>53</v>
-      </c>
-      <c r="H80" t="s">
+      <c r="I89" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N89" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I80" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>165</v>
-      </c>
-      <c r="B81" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81" t="s">
-        <v>51</v>
-      </c>
-      <c r="F81" t="s">
-        <v>52</v>
-      </c>
-      <c r="G81" t="s">
-        <v>53</v>
-      </c>
-      <c r="H81" t="s">
-        <v>136</v>
-      </c>
-      <c r="I81" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>165</v>
-      </c>
-      <c r="B82" t="s">
-        <v>249</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
-        <v>51</v>
-      </c>
-      <c r="F82" t="s">
-        <v>52</v>
-      </c>
-      <c r="G82" t="s">
-        <v>53</v>
-      </c>
-      <c r="H82" t="s">
-        <v>138</v>
-      </c>
-      <c r="I82" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>165</v>
-      </c>
-      <c r="B83" t="s">
-        <v>250</v>
-      </c>
-      <c r="C83">
-        <v>7</v>
-      </c>
-      <c r="D83">
-        <v>7</v>
-      </c>
-      <c r="E83" t="s">
-        <v>51</v>
-      </c>
-      <c r="F83" t="s">
-        <v>52</v>
-      </c>
-      <c r="G83" t="s">
-        <v>53</v>
-      </c>
-      <c r="H83" t="s">
-        <v>140</v>
-      </c>
-      <c r="I83" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>165</v>
-      </c>
-      <c r="B84" t="s">
-        <v>253</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
-        <v>51</v>
-      </c>
-      <c r="F84" t="s">
-        <v>52</v>
-      </c>
-      <c r="G84" t="s">
-        <v>53</v>
-      </c>
-      <c r="H84" t="s">
-        <v>142</v>
-      </c>
-      <c r="I84" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>165</v>
-      </c>
-      <c r="B85" t="s">
-        <v>256</v>
-      </c>
-      <c r="C85">
-        <v>5</v>
-      </c>
-      <c r="D85">
-        <v>5</v>
-      </c>
-      <c r="E85" t="s">
-        <v>51</v>
-      </c>
-      <c r="F85" t="s">
-        <v>52</v>
-      </c>
-      <c r="G85" t="s">
-        <v>53</v>
-      </c>
-      <c r="H85" t="s">
-        <v>144</v>
-      </c>
-      <c r="I85" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>165</v>
-      </c>
-      <c r="B86" t="s">
-        <v>259</v>
-      </c>
-      <c r="C86">
-        <v>2</v>
-      </c>
-      <c r="D86">
-        <v>2</v>
-      </c>
-      <c r="E86" t="s">
-        <v>51</v>
-      </c>
-      <c r="F86" t="s">
-        <v>52</v>
-      </c>
-      <c r="G86" t="s">
-        <v>53</v>
-      </c>
-      <c r="H86" t="s">
-        <v>146</v>
-      </c>
-      <c r="I86" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>165</v>
-      </c>
-      <c r="B87" t="s">
-        <v>261</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-      <c r="E87" t="s">
-        <v>51</v>
-      </c>
-      <c r="F87" t="s">
-        <v>52</v>
-      </c>
-      <c r="G87" t="s">
-        <v>53</v>
-      </c>
-      <c r="H87" t="s">
-        <v>148</v>
-      </c>
-      <c r="I87" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>165</v>
-      </c>
-      <c r="B88" t="s">
-        <v>262</v>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-      <c r="D88">
-        <v>2</v>
-      </c>
-      <c r="E88" t="s">
-        <v>51</v>
-      </c>
-      <c r="F88" t="s">
-        <v>52</v>
-      </c>
-      <c r="G88" t="s">
-        <v>53</v>
-      </c>
-      <c r="H88" t="s">
-        <v>150</v>
-      </c>
-      <c r="I88" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>165</v>
-      </c>
-      <c r="B89" t="s">
-        <v>263</v>
-      </c>
-      <c r="C89">
-        <v>2</v>
-      </c>
-      <c r="D89">
-        <v>2</v>
-      </c>
-      <c r="E89" t="s">
-        <v>51</v>
-      </c>
-      <c r="F89" t="s">
-        <v>52</v>
-      </c>
-      <c r="G89" t="s">
-        <v>53</v>
-      </c>
-      <c r="H89" t="s">
-        <v>54</v>
-      </c>
-      <c r="I89" t="s">
-        <v>152</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C2:D89" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>